--- a/outputs/57113.xlsx
+++ b/outputs/57113.xlsx
@@ -107,8 +107,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -304,40 +308,40 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="51.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="51.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="str">
-        <f aca="false">IFERROR(SUBSTITUTE(TRIM(LEFT(SUBSTITUTE(MID(A2,FIND("#",A2),LEN(A2))," ",REPT(" ",100)),100)),"#",""),"")</f>
+      <c r="B2" s="1" t="str">
+        <f aca="false">TRIM(LEFT(SUBSTITUTE(MID(A2,FIND("#",A2)+1,LEN(A2))," ",REPT(" ",100)),100))</f>
         <v>Corn</v>
       </c>
-      <c r="C2" s="0" t="str">
-        <f aca="false">IFERROR(SUBSTITUTE(TRIM(LEFT(SUBSTITUTE(MID(A2,FIND(CHAR(1),SUBSTITUTE(A2,"#",CHAR(1),2)),LEN(A2))," ",REPT(" ",100)),100)),"#",""),"")</f>
+      <c r="C2" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(FIND("#",A2,FIND("#",A2)+1)),TRIM(LEFT(SUBSTITUTE(MID(A2,FIND("#",A2,FIND("#",A2)+1)+1,LEN(A2))," ",REPT(" ",100)),100)),"")</f>
         <v/>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="0" t="str">
-        <f aca="false">IFERROR(SUBSTITUTE(TRIM(LEFT(SUBSTITUTE(MID(A3,FIND("#",A3),LEN(A3))," ",REPT(" ",100)),100)),"#",""),"")</f>
+      <c r="B3" s="1" t="str">
+        <f aca="false">TRIM(LEFT(SUBSTITUTE(MID(A3,FIND("#",A3)+1,LEN(A3))," ",REPT(" ",100)),100))</f>
         <v>tomatoes</v>
       </c>
-      <c r="C3" s="0" t="str">
-        <f aca="false">IFERROR(SUBSTITUTE(TRIM(LEFT(SUBSTITUTE(MID(A3,FIND(CHAR(1),SUBSTITUTE(A3,"#",CHAR(1),2)),LEN(A3))," ",REPT(" ",100)),100)),"#",""),"")</f>
+      <c r="C3" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(FIND("#",A3,FIND("#",A3)+1)),TRIM(LEFT(SUBSTITUTE(MID(A3,FIND("#",A3,FIND("#",A3)+1)+1,LEN(A3))," ",REPT(" ",100)),100)),"")</f>
         <v>vegetables</v>
       </c>
     </row>

--- a/outputs/57113.xlsx
+++ b/outputs/57113.xlsx
@@ -1,19 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -22,121 +29,701 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t xml:space="preserve">Tweet</t>
+    <t>Tweet</t>
   </si>
   <si>
-    <t xml:space="preserve">Hashtag</t>
+    <t>Hashtag</t>
   </si>
   <si>
-    <t xml:space="preserve">Corn is great #Corn I love it</t>
+    <t>Corn is great #Corn I love it</t>
   </si>
   <si>
-    <t xml:space="preserve">Tomatoes are great #tomatoes I love them #vegetables yum</t>
+    <t>Tomatoes are great #tomatoes I love them #vegetables yum</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="0"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="9">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -171,55 +758,119 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -227,24 +878,33 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -257,7 +917,13 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -267,13 +933,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
+                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -281,6 +949,7 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
+                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -288,70 +957,64 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="51.36"/>
+    <col min="1" max="1" width="51.3666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="str">
-        <f aca="false">TRIM(LEFT(SUBSTITUTE(MID(A2,FIND("#",A2)+1,LEN(A2))," ",REPT(" ",100)),100))</f>
-        <v>Corn</v>
+      <c r="B2" t="str">
+        <f>TRIM(LEFT(SUBSTITUTE(MID(A2,FIND("#",A2),LEN(A2))," ",REPT(" ",100)),100))</f>
+        <v>#Corn</v>
       </c>
-      <c r="C2" s="1" t="str">
-        <f aca="false">IF(ISNUMBER(FIND("#",A2,FIND("#",A2)+1)),TRIM(LEFT(SUBSTITUTE(MID(A2,FIND("#",A2,FIND("#",A2)+1)+1,LEN(A2))," ",REPT(" ",100)),100)),"")</f>
-        <v/>
+      <c r="C2" t="str">
+        <f>TRIM(LEFT(SUBSTITUTE(MID(B2,FIND("#",B2),LEN(B2))," ",REPT(" ",100)),100))</f>
+        <v>#Corn</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="str">
-        <f aca="false">TRIM(LEFT(SUBSTITUTE(MID(A3,FIND("#",A3)+1,LEN(A3))," ",REPT(" ",100)),100))</f>
-        <v>tomatoes</v>
+      <c r="B3" t="str">
+        <f>TRIM(LEFT(SUBSTITUTE(MID(A3,FIND("#",A3),LEN(A3))," ",REPT(" ",100)),100))</f>
+        <v>#tomatoes</v>
       </c>
-      <c r="C3" s="1" t="str">
-        <f aca="false">IF(ISNUMBER(FIND("#",A3,FIND("#",A3)+1)),TRIM(LEFT(SUBSTITUTE(MID(A3,FIND("#",A3,FIND("#",A3)+1)+1,LEN(A3))," ",REPT(" ",100)),100)),"")</f>
-        <v>vegetables</v>
+      <c r="C3" t="str">
+        <f>TRIM(LEFT(SUBSTITUTE(MID(B3,FIND("#",B3),LEN(B3))," ",REPT(" ",100)),100))</f>
+        <v>#tomatoes</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>